--- a/forms/trg/Formulir_TRG_sssn.xlsx
+++ b/forms/trg/Formulir_TRG_sssn.xlsx
@@ -975,7 +975,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
